--- a/artfynd/A 26733-2024 artfynd.xlsx
+++ b/artfynd/A 26733-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136348932</v>
       </c>
       <c r="B2" t="n">
-        <v>92281</v>
+        <v>92284</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1673,7 +1673,7 @@
         <v>136348931</v>
       </c>
       <c r="B11" t="n">
-        <v>93416</v>
+        <v>93419</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2006,7 +2006,7 @@
         <v>136348925</v>
       </c>
       <c r="B14" t="n">
-        <v>93392</v>
+        <v>93395</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2117,7 +2117,7 @@
         <v>136348926</v>
       </c>
       <c r="B15" t="n">
-        <v>93392</v>
+        <v>93395</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2228,7 +2228,7 @@
         <v>136348930</v>
       </c>
       <c r="B16" t="n">
-        <v>93392</v>
+        <v>93395</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2561,7 +2561,7 @@
         <v>136348924</v>
       </c>
       <c r="B19" t="n">
-        <v>93394</v>
+        <v>93397</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3021,7 +3021,7 @@
         <v>136348929</v>
       </c>
       <c r="B23" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3132,7 +3132,7 @@
         <v>136348936</v>
       </c>
       <c r="B24" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3243,7 +3243,7 @@
         <v>136348937</v>
       </c>
       <c r="B25" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3567,7 +3567,7 @@
         <v>136348933</v>
       </c>
       <c r="B28" t="n">
-        <v>93404</v>
+        <v>93407</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4011,7 +4011,7 @@
         <v>136348934</v>
       </c>
       <c r="B32" t="n">
-        <v>93412</v>
+        <v>93415</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4122,7 +4122,7 @@
         <v>136348935</v>
       </c>
       <c r="B33" t="n">
-        <v>93412</v>
+        <v>93415</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4233,7 +4233,7 @@
         <v>136348940</v>
       </c>
       <c r="B34" t="n">
-        <v>93412</v>
+        <v>93415</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4344,7 +4344,7 @@
         <v>136348939</v>
       </c>
       <c r="B35" t="n">
-        <v>93044</v>
+        <v>93047</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4899,7 +4899,7 @@
         <v>136348938</v>
       </c>
       <c r="B40" t="n">
-        <v>93438</v>
+        <v>93441</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>

--- a/artfynd/A 26733-2024 artfynd.xlsx
+++ b/artfynd/A 26733-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136348932</v>
       </c>
       <c r="B2" t="n">
-        <v>92284</v>
+        <v>92285</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1673,7 +1673,7 @@
         <v>136348931</v>
       </c>
       <c r="B11" t="n">
-        <v>93419</v>
+        <v>93420</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2006,7 +2006,7 @@
         <v>136348925</v>
       </c>
       <c r="B14" t="n">
-        <v>93395</v>
+        <v>93396</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2117,7 +2117,7 @@
         <v>136348926</v>
       </c>
       <c r="B15" t="n">
-        <v>93395</v>
+        <v>93396</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2228,7 +2228,7 @@
         <v>136348930</v>
       </c>
       <c r="B16" t="n">
-        <v>93395</v>
+        <v>93396</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2561,7 +2561,7 @@
         <v>136348924</v>
       </c>
       <c r="B19" t="n">
-        <v>93397</v>
+        <v>93398</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3021,7 +3021,7 @@
         <v>136348929</v>
       </c>
       <c r="B23" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3132,7 +3132,7 @@
         <v>136348936</v>
       </c>
       <c r="B24" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3243,7 +3243,7 @@
         <v>136348937</v>
       </c>
       <c r="B25" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3567,7 +3567,7 @@
         <v>136348933</v>
       </c>
       <c r="B28" t="n">
-        <v>93407</v>
+        <v>93408</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4011,7 +4011,7 @@
         <v>136348934</v>
       </c>
       <c r="B32" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4122,7 +4122,7 @@
         <v>136348935</v>
       </c>
       <c r="B33" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4233,7 +4233,7 @@
         <v>136348940</v>
       </c>
       <c r="B34" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4344,7 +4344,7 @@
         <v>136348939</v>
       </c>
       <c r="B35" t="n">
-        <v>93047</v>
+        <v>93048</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4899,7 +4899,7 @@
         <v>136348938</v>
       </c>
       <c r="B40" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>

--- a/artfynd/A 26733-2024 artfynd.xlsx
+++ b/artfynd/A 26733-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136348932</v>
       </c>
       <c r="B2" t="n">
-        <v>92285</v>
+        <v>92290</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1673,7 +1673,7 @@
         <v>136348931</v>
       </c>
       <c r="B11" t="n">
-        <v>93420</v>
+        <v>93425</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2006,7 +2006,7 @@
         <v>136348925</v>
       </c>
       <c r="B14" t="n">
-        <v>93396</v>
+        <v>93401</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2117,7 +2117,7 @@
         <v>136348926</v>
       </c>
       <c r="B15" t="n">
-        <v>93396</v>
+        <v>93401</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2228,7 +2228,7 @@
         <v>136348930</v>
       </c>
       <c r="B16" t="n">
-        <v>93396</v>
+        <v>93401</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2561,7 +2561,7 @@
         <v>136348924</v>
       </c>
       <c r="B19" t="n">
-        <v>93398</v>
+        <v>93403</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3021,7 +3021,7 @@
         <v>136348929</v>
       </c>
       <c r="B23" t="n">
-        <v>93404</v>
+        <v>93409</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3132,7 +3132,7 @@
         <v>136348936</v>
       </c>
       <c r="B24" t="n">
-        <v>93404</v>
+        <v>93409</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3243,7 +3243,7 @@
         <v>136348937</v>
       </c>
       <c r="B25" t="n">
-        <v>93404</v>
+        <v>93409</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3567,7 +3567,7 @@
         <v>136348933</v>
       </c>
       <c r="B28" t="n">
-        <v>93408</v>
+        <v>93413</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4011,7 +4011,7 @@
         <v>136348934</v>
       </c>
       <c r="B32" t="n">
-        <v>93416</v>
+        <v>93421</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4122,7 +4122,7 @@
         <v>136348935</v>
       </c>
       <c r="B33" t="n">
-        <v>93416</v>
+        <v>93421</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4233,7 +4233,7 @@
         <v>136348940</v>
       </c>
       <c r="B34" t="n">
-        <v>93416</v>
+        <v>93421</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4344,7 +4344,7 @@
         <v>136348939</v>
       </c>
       <c r="B35" t="n">
-        <v>93048</v>
+        <v>93053</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4899,7 +4899,7 @@
         <v>136348938</v>
       </c>
       <c r="B40" t="n">
-        <v>93442</v>
+        <v>93447</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>

--- a/artfynd/A 26733-2024 artfynd.xlsx
+++ b/artfynd/A 26733-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136348932</v>
       </c>
       <c r="B2" t="n">
-        <v>92290</v>
+        <v>92292</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1673,7 +1673,7 @@
         <v>136348931</v>
       </c>
       <c r="B11" t="n">
-        <v>93425</v>
+        <v>93427</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2006,7 +2006,7 @@
         <v>136348925</v>
       </c>
       <c r="B14" t="n">
-        <v>93401</v>
+        <v>93403</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2117,7 +2117,7 @@
         <v>136348926</v>
       </c>
       <c r="B15" t="n">
-        <v>93401</v>
+        <v>93403</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2228,7 +2228,7 @@
         <v>136348930</v>
       </c>
       <c r="B16" t="n">
-        <v>93401</v>
+        <v>93403</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2561,7 +2561,7 @@
         <v>136348924</v>
       </c>
       <c r="B19" t="n">
-        <v>93403</v>
+        <v>93405</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3021,7 +3021,7 @@
         <v>136348929</v>
       </c>
       <c r="B23" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3132,7 +3132,7 @@
         <v>136348936</v>
       </c>
       <c r="B24" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3243,7 +3243,7 @@
         <v>136348937</v>
       </c>
       <c r="B25" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3567,7 +3567,7 @@
         <v>136348933</v>
       </c>
       <c r="B28" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4011,7 +4011,7 @@
         <v>136348934</v>
       </c>
       <c r="B32" t="n">
-        <v>93421</v>
+        <v>93423</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4122,7 +4122,7 @@
         <v>136348935</v>
       </c>
       <c r="B33" t="n">
-        <v>93421</v>
+        <v>93423</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4233,7 +4233,7 @@
         <v>136348940</v>
       </c>
       <c r="B34" t="n">
-        <v>93421</v>
+        <v>93423</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4344,7 +4344,7 @@
         <v>136348939</v>
       </c>
       <c r="B35" t="n">
-        <v>93053</v>
+        <v>93055</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4899,7 +4899,7 @@
         <v>136348938</v>
       </c>
       <c r="B40" t="n">
-        <v>93447</v>
+        <v>93449</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>

--- a/artfynd/A 26733-2024 artfynd.xlsx
+++ b/artfynd/A 26733-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136348932</v>
       </c>
       <c r="B2" t="n">
-        <v>92292</v>
+        <v>92294</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1673,7 +1673,7 @@
         <v>136348931</v>
       </c>
       <c r="B11" t="n">
-        <v>93427</v>
+        <v>93429</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2006,7 +2006,7 @@
         <v>136348925</v>
       </c>
       <c r="B14" t="n">
-        <v>93403</v>
+        <v>93405</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2117,7 +2117,7 @@
         <v>136348926</v>
       </c>
       <c r="B15" t="n">
-        <v>93403</v>
+        <v>93405</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2228,7 +2228,7 @@
         <v>136348930</v>
       </c>
       <c r="B16" t="n">
-        <v>93403</v>
+        <v>93405</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2561,7 +2561,7 @@
         <v>136348924</v>
       </c>
       <c r="B19" t="n">
-        <v>93405</v>
+        <v>93407</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3021,7 +3021,7 @@
         <v>136348929</v>
       </c>
       <c r="B23" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3132,7 +3132,7 @@
         <v>136348936</v>
       </c>
       <c r="B24" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3243,7 +3243,7 @@
         <v>136348937</v>
       </c>
       <c r="B25" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3567,7 +3567,7 @@
         <v>136348933</v>
       </c>
       <c r="B28" t="n">
-        <v>93415</v>
+        <v>93417</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4011,7 +4011,7 @@
         <v>136348934</v>
       </c>
       <c r="B32" t="n">
-        <v>93423</v>
+        <v>93425</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4122,7 +4122,7 @@
         <v>136348935</v>
       </c>
       <c r="B33" t="n">
-        <v>93423</v>
+        <v>93425</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4233,7 +4233,7 @@
         <v>136348940</v>
       </c>
       <c r="B34" t="n">
-        <v>93423</v>
+        <v>93425</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4344,7 +4344,7 @@
         <v>136348939</v>
       </c>
       <c r="B35" t="n">
-        <v>93055</v>
+        <v>93057</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4899,7 +4899,7 @@
         <v>136348938</v>
       </c>
       <c r="B40" t="n">
-        <v>93449</v>
+        <v>93451</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>

--- a/artfynd/A 26733-2024 artfynd.xlsx
+++ b/artfynd/A 26733-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136348932</v>
       </c>
       <c r="B2" t="n">
-        <v>92294</v>
+        <v>92296</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1673,7 +1673,7 @@
         <v>136348931</v>
       </c>
       <c r="B11" t="n">
-        <v>93429</v>
+        <v>93431</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2006,7 +2006,7 @@
         <v>136348925</v>
       </c>
       <c r="B14" t="n">
-        <v>93405</v>
+        <v>93407</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2117,7 +2117,7 @@
         <v>136348926</v>
       </c>
       <c r="B15" t="n">
-        <v>93405</v>
+        <v>93407</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2228,7 +2228,7 @@
         <v>136348930</v>
       </c>
       <c r="B16" t="n">
-        <v>93405</v>
+        <v>93407</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2561,7 +2561,7 @@
         <v>136348924</v>
       </c>
       <c r="B19" t="n">
-        <v>93407</v>
+        <v>93409</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3021,7 +3021,7 @@
         <v>136348929</v>
       </c>
       <c r="B23" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3132,7 +3132,7 @@
         <v>136348936</v>
       </c>
       <c r="B24" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3243,7 +3243,7 @@
         <v>136348937</v>
       </c>
       <c r="B25" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3567,7 +3567,7 @@
         <v>136348933</v>
       </c>
       <c r="B28" t="n">
-        <v>93417</v>
+        <v>93419</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4011,7 +4011,7 @@
         <v>136348934</v>
       </c>
       <c r="B32" t="n">
-        <v>93425</v>
+        <v>93427</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4122,7 +4122,7 @@
         <v>136348935</v>
       </c>
       <c r="B33" t="n">
-        <v>93425</v>
+        <v>93427</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4233,7 +4233,7 @@
         <v>136348940</v>
       </c>
       <c r="B34" t="n">
-        <v>93425</v>
+        <v>93427</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4344,7 +4344,7 @@
         <v>136348939</v>
       </c>
       <c r="B35" t="n">
-        <v>93057</v>
+        <v>93059</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4899,7 +4899,7 @@
         <v>136348938</v>
       </c>
       <c r="B40" t="n">
-        <v>93451</v>
+        <v>93453</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
